--- a/factory/工厂配送麦安研门店周度销售报表_格式化模板.xlsx
+++ b/factory/工厂配送麦安研门店周度销售报表_格式化模板.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wadec\Documents\Projects\mainyan-auto\factory\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wadec\Documents\projects\mainyan-auto\factory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D03BEC31-4280-47D8-9EDA-A72E92596428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0830496-726A-43FF-8111-60BB7862B8F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="841" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12756" yWindow="0" windowWidth="10380" windowHeight="12336" tabRatio="841" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="货品对比表6.8-6.14" sheetId="1" r:id="rId1"/>
@@ -119,7 +119,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="0.00_ "/>
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -280,30 +280,51 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -311,27 +332,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -825,241 +825,241 @@
   <dimension ref="A1:R18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.6640625" style="8" customWidth="1"/>
-    <col min="2" max="2" width="20.21875" style="8" customWidth="1"/>
-    <col min="3" max="3" width="9.44140625" style="8" customWidth="1"/>
-    <col min="4" max="4" width="26.33203125" style="8" customWidth="1"/>
-    <col min="5" max="5" width="20.88671875" style="8" customWidth="1"/>
-    <col min="6" max="6" width="4.6640625" style="16" customWidth="1"/>
-    <col min="7" max="7" width="8.77734375" style="16" customWidth="1"/>
-    <col min="8" max="8" width="10.21875" style="17" customWidth="1"/>
-    <col min="9" max="9" width="8.21875" style="16" customWidth="1"/>
-    <col min="10" max="10" width="10.6640625" style="17" customWidth="1"/>
-    <col min="11" max="11" width="8.44140625" style="16" customWidth="1"/>
-    <col min="12" max="12" width="10.6640625" style="17" customWidth="1"/>
-    <col min="13" max="13" width="8.88671875" style="16" customWidth="1"/>
-    <col min="14" max="14" width="10.6640625" style="17" customWidth="1"/>
-    <col min="15" max="15" width="8.21875" style="16" customWidth="1"/>
-    <col min="16" max="16" width="10.6640625" style="17" customWidth="1"/>
-    <col min="17" max="17" width="9" style="8"/>
-    <col min="18" max="18" width="11.109375" style="8"/>
-    <col min="19" max="16384" width="9" style="8"/>
+    <col min="1" max="1" width="4.6640625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="20.21875" style="6" customWidth="1"/>
+    <col min="3" max="3" width="9.44140625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="26.33203125" style="6" customWidth="1"/>
+    <col min="5" max="5" width="20.88671875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="4.6640625" style="11" customWidth="1"/>
+    <col min="7" max="7" width="8.77734375" style="11" customWidth="1"/>
+    <col min="8" max="8" width="11.5546875" style="12" customWidth="1"/>
+    <col min="9" max="9" width="8.21875" style="11" customWidth="1"/>
+    <col min="10" max="10" width="10.6640625" style="12" customWidth="1"/>
+    <col min="11" max="11" width="8.44140625" style="11" customWidth="1"/>
+    <col min="12" max="12" width="10.6640625" style="12" customWidth="1"/>
+    <col min="13" max="13" width="8.88671875" style="11" customWidth="1"/>
+    <col min="14" max="14" width="10.6640625" style="12" customWidth="1"/>
+    <col min="15" max="15" width="8.21875" style="11" customWidth="1"/>
+    <col min="16" max="16" width="10.6640625" style="12" customWidth="1"/>
+    <col min="17" max="17" width="9" style="6"/>
+    <col min="18" max="18" width="11.109375" style="6"/>
+    <col min="19" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="3" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
     </row>
     <row r="2" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="L2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="M2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="N2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="7" t="s">
+      <c r="P2" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="5">
-        <f>SUM(G4:G6)</f>
-        <v>0</v>
-      </c>
-      <c r="H3" s="6">
-        <f>SUM(H4:H6)</f>
-        <v>0</v>
-      </c>
-      <c r="I3" s="5">
-        <f>SUM(I4:I6)</f>
-        <v>0</v>
-      </c>
-      <c r="J3" s="7">
-        <f>SUM(J4:J6)</f>
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <f>SUM(K4:K6)</f>
-        <v>0</v>
-      </c>
-      <c r="L3" s="7">
-        <f>SUM(L4:L6)</f>
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <f>SUM(M4:M6)</f>
-        <v>0</v>
-      </c>
-      <c r="N3" s="7">
-        <f>SUM(N4:N6)</f>
-        <v>0</v>
-      </c>
-      <c r="O3" s="5">
-        <f>SUM(O4:O6)</f>
-        <v>0</v>
-      </c>
-      <c r="P3" s="7">
-        <f>SUM(P4:P6)</f>
-        <v>0</v>
-      </c>
-      <c r="R3" s="14"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="3">
+        <f t="shared" ref="G3:P3" si="0">SUM(G4:G6)</f>
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I3" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K3" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M3" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O3" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P3" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R3" s="9"/>
     </row>
     <row r="4" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
+      <c r="A4" s="3">
         <f>ROW()-3</f>
         <v>1</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5">
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3">
         <f>SUM(I4,K4,M4,O4)</f>
         <v>0</v>
       </c>
-      <c r="H4" s="18">
+      <c r="H4" s="13">
         <f>SUM(J4,L4,N4,P4)</f>
         <v>0</v>
       </c>
-      <c r="I4" s="5"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="7"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="5"/>
     </row>
     <row r="5" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
-        <f t="shared" ref="A5" si="0">ROW()-3</f>
+      <c r="A5" s="3">
+        <f t="shared" ref="A5" si="1">ROW()-3</f>
         <v>2</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5">
-        <f t="shared" ref="G5:G6" si="1">SUM(I5,K5,M5,O5)</f>
-        <v>0</v>
-      </c>
-      <c r="H5" s="18">
-        <f t="shared" ref="H5:H6" si="2">SUM(J5,L5,N5,P5)</f>
-        <v>0</v>
-      </c>
-      <c r="I5" s="5"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="7"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3">
+        <f t="shared" ref="G5:G6" si="2">SUM(I5,K5,M5,O5)</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="13">
+        <f t="shared" ref="H5:H6" si="3">SUM(J5,L5,N5,P5)</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="3"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="5"/>
     </row>
     <row r="6" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5">
-        <f t="shared" ref="A6" si="3">ROW()-3</f>
+      <c r="A6" s="3">
+        <f t="shared" ref="A6" si="4">ROW()-3</f>
         <v>3</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H6" s="18">
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I6" s="5"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="7"/>
-    </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" s="15" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" s="15" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="H6" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I6" s="3"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="5"/>
+    </row>
+    <row r="7" spans="1:18" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:18" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:18" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:18" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:18" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:18" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:18" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:18" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:18" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:18" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:P1"/>
@@ -1075,124 +1075,124 @@
   <dimension ref="A1:H18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.6640625" style="8" customWidth="1"/>
-    <col min="2" max="2" width="20.21875" style="8" customWidth="1"/>
-    <col min="3" max="3" width="9.44140625" style="8" customWidth="1"/>
-    <col min="4" max="4" width="26.33203125" style="8" customWidth="1"/>
-    <col min="5" max="5" width="20.88671875" style="8" customWidth="1"/>
-    <col min="6" max="6" width="4.6640625" style="16" customWidth="1"/>
-    <col min="7" max="7" width="8.77734375" style="16" customWidth="1"/>
-    <col min="8" max="8" width="10.21875" style="17" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="8"/>
+    <col min="1" max="1" width="4.6640625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="20.21875" style="6" customWidth="1"/>
+    <col min="3" max="3" width="9.44140625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="26.33203125" style="6" customWidth="1"/>
+    <col min="5" max="5" width="20.88671875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="4.6640625" style="11" customWidth="1"/>
+    <col min="7" max="7" width="8.77734375" style="11" customWidth="1"/>
+    <col min="8" max="8" width="10.21875" style="12" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="3" customFormat="1" ht="28.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" s="1" customFormat="1" ht="28.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="5">
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="3">
         <f>SUM(G4:G6)</f>
         <v>0</v>
       </c>
-      <c r="H3" s="12">
+      <c r="H3" s="7">
         <f>SUM(H4:H6)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
+      <c r="A4" s="3">
         <f>ROW()-3</f>
         <v>1</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="6"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
+      <c r="A5" s="3">
         <f t="shared" ref="A5:A6" si="0">ROW()-3</f>
         <v>2</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="6"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="4"/>
     </row>
     <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5">
+      <c r="A6" s="3">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="6"/>
-    </row>
-    <row r="7" spans="1:8" s="15" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:8" s="15" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="1:8" s="15" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:8" s="15" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:8" s="15" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:8" s="15" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:8" s="15" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:8" s="15" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:8" s="15" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:8" s="15" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" s="15" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" s="15" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" spans="1:8" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:8" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:8" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:8" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:8" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:8" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:8" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:8" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:8" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:8" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:H18">
     <sortCondition descending="1" ref="H3"/>
@@ -1212,124 +1212,124 @@
   <dimension ref="A1:H18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.6640625" style="8" customWidth="1"/>
-    <col min="2" max="2" width="20.21875" style="8" customWidth="1"/>
-    <col min="3" max="3" width="9.44140625" style="8" customWidth="1"/>
-    <col min="4" max="4" width="26.33203125" style="8" customWidth="1"/>
-    <col min="5" max="5" width="20.88671875" style="8" customWidth="1"/>
-    <col min="6" max="6" width="4.6640625" style="16" customWidth="1"/>
-    <col min="7" max="7" width="8.21875" style="16" customWidth="1"/>
-    <col min="8" max="8" width="10.6640625" style="17" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="8"/>
+    <col min="1" max="1" width="4.6640625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="20.21875" style="6" customWidth="1"/>
+    <col min="3" max="3" width="9.44140625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="26.33203125" style="6" customWidth="1"/>
+    <col min="5" max="5" width="20.88671875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="4.6640625" style="11" customWidth="1"/>
+    <col min="7" max="7" width="8.21875" style="11" customWidth="1"/>
+    <col min="8" max="8" width="10.6640625" style="12" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="5">
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="3">
         <f>SUM(G4:G6)</f>
         <v>0</v>
       </c>
-      <c r="H3" s="13">
+      <c r="H3" s="8">
         <f>SUM(H4:H6)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
+      <c r="A4" s="3">
         <f>ROW()-3</f>
         <v>1</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="7"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="5"/>
     </row>
     <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
+      <c r="A5" s="3">
         <f t="shared" ref="A5:A6" si="0">ROW()-3</f>
         <v>2</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="7"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="5"/>
     </row>
     <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5">
+      <c r="A6" s="3">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="7"/>
-    </row>
-    <row r="7" spans="1:8" s="15" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:8" s="15" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="1:8" s="15" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:8" s="15" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:8" s="15" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:8" s="15" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:8" s="15" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:8" s="15" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:8" s="15" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:8" s="15" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" s="15" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" s="15" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="5"/>
+    </row>
+    <row r="7" spans="1:8" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:8" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:8" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:8" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:8" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:8" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:8" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:8" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:8" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:8" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:H103">
     <sortCondition descending="1" ref="H3"/>

--- a/factory/工厂配送麦安研门店周度销售报表_格式化模板.xlsx
+++ b/factory/工厂配送麦安研门店周度销售报表_格式化模板.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0830496-726A-43FF-8111-60BB7862B8F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12756" yWindow="0" windowWidth="10380" windowHeight="12336" tabRatio="841" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="841" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="货品对比表6.8-6.14" sheetId="1" r:id="rId1"/>
